--- a/pages/apps/uprn-service/info-descriptions.xlsx
+++ b/pages/apps/uprn-service/info-descriptions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NDSH\GitHub\dsh-content\dev\pages\apps\uprn-service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A615B9-8CA3-4BAF-AAEE-30804778314A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D847920-EB5C-4489-AD8F-7D4AD0DFB5E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="434" xr2:uid="{B9F83075-144E-4BA5-8EC2-97041BBCD0BC}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="434" xr2:uid="{B9F83075-144E-4BA5-8EC2-97041BBCD0BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -507,7 +507,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -526,6 +526,18 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -539,14 +551,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -882,13 +897,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78449B0B-0D1A-40FB-A65A-E443C6F99D5D}">
   <dimension ref="A1:C83"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="72.1796875" customWidth="1"/>
-    <col min="3" max="3" width="92.6328125" customWidth="1"/>
+    <col min="2" max="2" width="72.21875" customWidth="1"/>
+    <col min="3" max="3" width="92.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -899,7 +914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -910,7 +925,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -921,7 +936,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -932,7 +947,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -943,7 +958,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -954,7 +969,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -965,7 +980,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>9</v>
       </c>
@@ -976,7 +991,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>11</v>
       </c>
@@ -987,7 +1002,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>13</v>
       </c>
@@ -998,7 +1013,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>14</v>
       </c>
@@ -1009,7 +1024,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>15</v>
       </c>
@@ -1020,7 +1035,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>16</v>
       </c>
@@ -1031,7 +1046,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>17</v>
       </c>
@@ -1042,7 +1057,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>18</v>
       </c>
@@ -1053,7 +1068,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>19</v>
       </c>
@@ -1064,7 +1079,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>20</v>
       </c>
@@ -1075,7 +1090,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>21</v>
       </c>
@@ -1086,7 +1101,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>22</v>
       </c>
@@ -1097,7 +1112,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>23</v>
       </c>
@@ -1108,7 +1123,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>24</v>
       </c>
@@ -1119,7 +1134,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>25</v>
       </c>
@@ -1130,7 +1145,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>26</v>
       </c>
@@ -1141,7 +1156,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>27</v>
       </c>
@@ -1152,7 +1167,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>28</v>
       </c>
@@ -1163,7 +1178,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>29</v>
       </c>
@@ -1174,7 +1189,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>30</v>
       </c>
@@ -1185,7 +1200,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>31</v>
       </c>
@@ -1196,7 +1211,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>32</v>
       </c>
@@ -1207,7 +1222,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>33</v>
       </c>
@@ -1218,7 +1233,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>34</v>
       </c>
@@ -1229,7 +1244,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>35</v>
       </c>
@@ -1240,7 +1255,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>36</v>
       </c>
@@ -1251,7 +1266,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>37</v>
       </c>
@@ -1262,7 +1277,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>38</v>
       </c>
@@ -1273,7 +1288,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>39</v>
       </c>
@@ -1284,7 +1299,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>40</v>
       </c>
@@ -1295,7 +1310,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>41</v>
       </c>
@@ -1306,7 +1321,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>42</v>
       </c>
@@ -1317,7 +1332,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>43</v>
       </c>
@@ -1328,7 +1343,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>44</v>
       </c>
@@ -1339,7 +1354,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>45</v>
       </c>
@@ -1350,7 +1365,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>46</v>
       </c>
@@ -1361,7 +1376,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>47</v>
       </c>
@@ -1372,7 +1387,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>48</v>
       </c>
@@ -1383,7 +1398,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>49</v>
       </c>
@@ -1394,7 +1409,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>50</v>
       </c>
@@ -1405,7 +1420,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>51</v>
       </c>
@@ -1416,7 +1431,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>52</v>
       </c>
@@ -1427,7 +1442,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>53</v>
       </c>
@@ -1438,7 +1453,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>101</v>
       </c>
@@ -1449,7 +1464,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>102</v>
       </c>
@@ -1460,7 +1475,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>103</v>
       </c>
@@ -1471,7 +1486,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>104</v>
       </c>
@@ -1482,7 +1497,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>105</v>
       </c>
@@ -1493,7 +1508,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>106</v>
       </c>
@@ -1504,7 +1519,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>107</v>
       </c>
@@ -1515,7 +1530,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>108</v>
       </c>
@@ -1526,7 +1541,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>109</v>
       </c>
@@ -1537,7 +1552,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>110</v>
       </c>
@@ -1548,18 +1563,18 @@
         <v>23</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>111</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="C61" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>112</v>
       </c>
@@ -1570,7 +1585,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>113</v>
       </c>
@@ -1581,7 +1596,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>114</v>
       </c>
@@ -1592,7 +1607,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>115</v>
       </c>
@@ -1603,7 +1618,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>116</v>
       </c>
@@ -1614,7 +1629,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>117</v>
       </c>
@@ -1625,7 +1640,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>118</v>
       </c>
@@ -1636,7 +1651,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
         <v>119</v>
       </c>
@@ -1647,7 +1662,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>120</v>
       </c>
@@ -1658,18 +1673,18 @@
         <v>50</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A71" s="2">
+    <row r="71" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="6">
         <v>121</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B71" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>122</v>
       </c>
@@ -1680,7 +1695,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>123</v>
       </c>
@@ -1691,18 +1706,18 @@
         <v>52</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A74" s="2">
+    <row r="74" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="6">
         <v>128</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B74" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>130</v>
       </c>
@@ -1713,7 +1728,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>131</v>
       </c>
@@ -1724,7 +1739,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>132</v>
       </c>
@@ -1735,29 +1750,29 @@
         <v>68</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A78" s="2">
+    <row r="78" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="8">
         <v>133</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="B78" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" s="8" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A79" s="2">
+    <row r="79" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="8">
         <v>134</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="B79" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="C79" s="8" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>201</v>
       </c>
@@ -1768,7 +1783,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>202</v>
       </c>
@@ -1779,7 +1794,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>203</v>
       </c>
@@ -1790,7 +1805,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>204</v>
       </c>
